--- a/2026--TSOSI-data-schema-institution-template.xlsx
+++ b/2026--TSOSI-data-schema-institution-template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Fields documentation" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Transfers!$A$1:$I$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Transfers!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t xml:space="preserve">infrastructure/name</t>
   </si>
@@ -53,6 +53,9 @@
     <t xml:space="preserve">contract/date_end</t>
   </si>
   <si>
+    <t xml:space="preserve">support_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Field</t>
   </si>
   <si>
@@ -84,6 +87,9 @@
   </si>
   <si>
     <t xml:space="preserve">If any, the end date of the contract. It usually to the start date of the support agreement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of support. Choose between : sponsorship, membership, service fee, grant or project funding, support, collaboration agreement, donation or other.</t>
   </si>
   <si>
     <t xml:space="preserve">Dates</t>
@@ -577,7 +583,9 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
@@ -606,7 +614,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:I42"/>
+  <autoFilter ref="A1:J1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -633,10 +641,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="4"/>
     </row>
@@ -645,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -660,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -675,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -690,7 +698,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -705,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -720,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -735,7 +743,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -750,7 +758,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -765,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -775,7 +783,13 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -831,10 +845,10 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -847,7 +861,7 @@
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
       <c r="B18" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
